--- a/data/final/series/bcb_sgs_ibc_br_sa.xlsx
+++ b/data/final/series/bcb_sgs_ibc_br_sa.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B59"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,7 +437,7 @@
         <v>44469</v>
       </c>
       <c r="B2" t="n">
-        <v>96.95313</v>
+        <v>96.96513</v>
       </c>
     </row>
     <row r="3">
@@ -445,7 +445,7 @@
         <v>44500</v>
       </c>
       <c r="B3" t="n">
-        <v>97.47790999999999</v>
+        <v>97.48671</v>
       </c>
     </row>
     <row r="4">
@@ -453,7 +453,7 @@
         <v>44530</v>
       </c>
       <c r="B4" t="n">
-        <v>99.05295</v>
+        <v>99.05526</v>
       </c>
     </row>
     <row r="5">
@@ -461,7 +461,7 @@
         <v>44561</v>
       </c>
       <c r="B5" t="n">
-        <v>99.36759000000001</v>
+        <v>99.37716</v>
       </c>
     </row>
     <row r="6">
@@ -469,7 +469,7 @@
         <v>44592</v>
       </c>
       <c r="B6" t="n">
-        <v>97.41759</v>
+        <v>97.4213</v>
       </c>
     </row>
     <row r="7">
@@ -477,7 +477,7 @@
         <v>44620</v>
       </c>
       <c r="B7" t="n">
-        <v>98.48287000000001</v>
+        <v>98.4804</v>
       </c>
     </row>
     <row r="8">
@@ -485,7 +485,7 @@
         <v>44651</v>
       </c>
       <c r="B8" t="n">
-        <v>99.54331000000001</v>
+        <v>99.54801999999999</v>
       </c>
     </row>
     <row r="9">
@@ -493,7 +493,7 @@
         <v>44681</v>
       </c>
       <c r="B9" t="n">
-        <v>99.44726</v>
+        <v>99.44118</v>
       </c>
     </row>
     <row r="10">
@@ -501,7 +501,7 @@
         <v>44712</v>
       </c>
       <c r="B10" t="n">
-        <v>99.65249</v>
+        <v>99.6454</v>
       </c>
     </row>
     <row r="11">
@@ -509,7 +509,7 @@
         <v>44742</v>
       </c>
       <c r="B11" t="n">
-        <v>99.53077999999999</v>
+        <v>99.51048</v>
       </c>
     </row>
     <row r="12">
@@ -517,7 +517,7 @@
         <v>44773</v>
       </c>
       <c r="B12" t="n">
-        <v>101.43252</v>
+        <v>101.43172</v>
       </c>
     </row>
     <row r="13">
@@ -525,7 +525,7 @@
         <v>44804</v>
       </c>
       <c r="B13" t="n">
-        <v>101.09886</v>
+        <v>101.10583</v>
       </c>
     </row>
     <row r="14">
@@ -533,7 +533,7 @@
         <v>44834</v>
       </c>
       <c r="B14" t="n">
-        <v>101.15209</v>
+        <v>101.16034</v>
       </c>
     </row>
     <row r="15">
@@ -541,7 +541,7 @@
         <v>44865</v>
       </c>
       <c r="B15" t="n">
-        <v>101.43094</v>
+        <v>101.44171</v>
       </c>
     </row>
     <row r="16">
@@ -549,7 +549,7 @@
         <v>44895</v>
       </c>
       <c r="B16" t="n">
-        <v>100.7113</v>
+        <v>100.7146</v>
       </c>
     </row>
     <row r="17">
@@ -557,7 +557,7 @@
         <v>44926</v>
       </c>
       <c r="B17" t="n">
-        <v>100.58566</v>
+        <v>100.58818</v>
       </c>
     </row>
     <row r="18">
@@ -565,7 +565,7 @@
         <v>44957</v>
       </c>
       <c r="B18" t="n">
-        <v>100.10937</v>
+        <v>100.10988</v>
       </c>
     </row>
     <row r="19">
@@ -573,7 +573,7 @@
         <v>44985</v>
       </c>
       <c r="B19" t="n">
-        <v>103.08344</v>
+        <v>103.07987</v>
       </c>
     </row>
     <row r="20">
@@ -581,7 +581,7 @@
         <v>45016</v>
       </c>
       <c r="B20" t="n">
-        <v>103.08526</v>
+        <v>103.08494</v>
       </c>
     </row>
     <row r="21">
@@ -589,7 +589,7 @@
         <v>45046</v>
       </c>
       <c r="B21" t="n">
-        <v>103.96006</v>
+        <v>103.93573</v>
       </c>
     </row>
     <row r="22">
@@ -597,7 +597,7 @@
         <v>45077</v>
       </c>
       <c r="B22" t="n">
-        <v>102.40467</v>
+        <v>102.42973</v>
       </c>
     </row>
     <row r="23">
@@ -605,7 +605,7 @@
         <v>45107</v>
       </c>
       <c r="B23" t="n">
-        <v>102.4398</v>
+        <v>102.39935</v>
       </c>
     </row>
     <row r="24">
@@ -613,7 +613,7 @@
         <v>45138</v>
       </c>
       <c r="B24" t="n">
-        <v>102.89895</v>
+        <v>102.90686</v>
       </c>
     </row>
     <row r="25">
@@ -621,7 +621,7 @@
         <v>45169</v>
       </c>
       <c r="B25" t="n">
-        <v>102.48797</v>
+        <v>102.50239</v>
       </c>
     </row>
     <row r="26">
@@ -629,7 +629,7 @@
         <v>45199</v>
       </c>
       <c r="B26" t="n">
-        <v>102.50227</v>
+        <v>102.5153</v>
       </c>
     </row>
     <row r="27">
@@ -637,7 +637,7 @@
         <v>45230</v>
       </c>
       <c r="B27" t="n">
-        <v>102.83037</v>
+        <v>102.83959</v>
       </c>
     </row>
     <row r="28">
@@ -645,7 +645,7 @@
         <v>45260</v>
       </c>
       <c r="B28" t="n">
-        <v>103.58799</v>
+        <v>103.59456</v>
       </c>
     </row>
     <row r="29">
@@ -653,7 +653,7 @@
         <v>45291</v>
       </c>
       <c r="B29" t="n">
-        <v>104.88262</v>
+        <v>104.88818</v>
       </c>
     </row>
     <row r="30">
@@ -661,7 +661,7 @@
         <v>45322</v>
       </c>
       <c r="B30" t="n">
-        <v>104.47589</v>
+        <v>104.473</v>
       </c>
     </row>
     <row r="31">
@@ -669,7 +669,7 @@
         <v>45351</v>
       </c>
       <c r="B31" t="n">
-        <v>104.67291</v>
+        <v>104.65885</v>
       </c>
     </row>
     <row r="32">
@@ -677,7 +677,7 @@
         <v>45382</v>
       </c>
       <c r="B32" t="n">
-        <v>104.68779</v>
+        <v>104.6738</v>
       </c>
     </row>
     <row r="33">
@@ -685,7 +685,7 @@
         <v>45412</v>
       </c>
       <c r="B33" t="n">
-        <v>104.6751</v>
+        <v>104.62771</v>
       </c>
     </row>
     <row r="34">
@@ -693,7 +693,7 @@
         <v>45443</v>
       </c>
       <c r="B34" t="n">
-        <v>105.5521</v>
+        <v>105.60427</v>
       </c>
     </row>
     <row r="35">
@@ -701,7 +701,7 @@
         <v>45473</v>
       </c>
       <c r="B35" t="n">
-        <v>106.65779</v>
+        <v>106.5891</v>
       </c>
     </row>
     <row r="36">
@@ -709,7 +709,7 @@
         <v>45504</v>
       </c>
       <c r="B36" t="n">
-        <v>107.01873</v>
+        <v>107.06237</v>
       </c>
     </row>
     <row r="37">
@@ -717,7 +717,7 @@
         <v>45535</v>
       </c>
       <c r="B37" t="n">
-        <v>107.16697</v>
+        <v>107.19174</v>
       </c>
     </row>
     <row r="38">
@@ -725,7 +725,7 @@
         <v>45565</v>
       </c>
       <c r="B38" t="n">
-        <v>108.02415</v>
+        <v>108.04382</v>
       </c>
     </row>
     <row r="39">
@@ -733,7 +733,7 @@
         <v>45596</v>
       </c>
       <c r="B39" t="n">
-        <v>108.23273</v>
+        <v>108.2446</v>
       </c>
     </row>
     <row r="40">
@@ -741,7 +741,7 @@
         <v>45626</v>
       </c>
       <c r="B40" t="n">
-        <v>107.99539</v>
+        <v>108.00109</v>
       </c>
     </row>
     <row r="41">
@@ -749,7 +749,7 @@
         <v>45657</v>
       </c>
       <c r="B41" t="n">
-        <v>107.3722</v>
+        <v>107.37012</v>
       </c>
     </row>
     <row r="42">
@@ -757,7 +757,7 @@
         <v>45688</v>
       </c>
       <c r="B42" t="n">
-        <v>108.10202</v>
+        <v>108.09524</v>
       </c>
     </row>
     <row r="43">
@@ -765,7 +765,7 @@
         <v>45716</v>
       </c>
       <c r="B43" t="n">
-        <v>108.64347</v>
+        <v>108.62006</v>
       </c>
     </row>
     <row r="44">
@@ -773,7 +773,7 @@
         <v>45747</v>
       </c>
       <c r="B44" t="n">
-        <v>110.0586</v>
+        <v>110.03287</v>
       </c>
     </row>
     <row r="45">
@@ -781,7 +781,7 @@
         <v>45777</v>
       </c>
       <c r="B45" t="n">
-        <v>109.59971</v>
+        <v>109.52766</v>
       </c>
     </row>
     <row r="46">
@@ -789,7 +789,7 @@
         <v>45808</v>
       </c>
       <c r="B46" t="n">
-        <v>108.80425</v>
+        <v>108.8862</v>
       </c>
     </row>
     <row r="47">
@@ -797,7 +797,7 @@
         <v>45838</v>
       </c>
       <c r="B47" t="n">
-        <v>108.90168</v>
+        <v>108.80376</v>
       </c>
     </row>
     <row r="48">
@@ -805,7 +805,7 @@
         <v>45869</v>
       </c>
       <c r="B48" t="n">
-        <v>108.39998</v>
+        <v>108.49869</v>
       </c>
     </row>
     <row r="49">
@@ -813,7 +813,7 @@
         <v>45900</v>
       </c>
       <c r="B49" t="n">
-        <v>108.79892</v>
+        <v>108.82893</v>
       </c>
     </row>
     <row r="50">
@@ -821,7 +821,7 @@
         <v>45930</v>
       </c>
       <c r="B50" t="n">
-        <v>108.7209</v>
+        <v>108.73548</v>
       </c>
     </row>
     <row r="51">
@@ -829,7 +829,7 @@
         <v>45961</v>
       </c>
       <c r="B51" t="n">
-        <v>108.73364</v>
+        <v>108.75326</v>
       </c>
     </row>
     <row r="52">
@@ -837,7 +837,7 @@
         <v>45991</v>
       </c>
       <c r="B52" t="n">
-        <v>109.24151</v>
+        <v>109.25005</v>
       </c>
     </row>
     <row r="53">
@@ -845,7 +845,7 @@
         <v>46022</v>
       </c>
       <c r="B53" t="n">
-        <v>109.46142</v>
+        <v>109.4528</v>
       </c>
     </row>
     <row r="54">
@@ -853,7 +853,7 @@
         <v>46053</v>
       </c>
       <c r="B54" t="n">
-        <v>110.07661</v>
+        <v>110.04992</v>
       </c>
     </row>
     <row r="55">
@@ -861,7 +861,7 @@
         <v>46081</v>
       </c>
       <c r="B55" t="n">
-        <v>110.77581</v>
+        <v>110.7366</v>
       </c>
     </row>
     <row r="56">
@@ -869,7 +869,7 @@
         <v>46112</v>
       </c>
       <c r="B56" t="n">
-        <v>110.60765</v>
+        <v>110.58808</v>
       </c>
     </row>
     <row r="57">
@@ -877,7 +877,7 @@
         <v>46142</v>
       </c>
       <c r="B57" t="n">
-        <v>110.90086</v>
+        <v>110.90009</v>
       </c>
     </row>
     <row r="58">
@@ -885,7 +885,7 @@
         <v>46173</v>
       </c>
       <c r="B58" t="n">
-        <v>110.93102</v>
+        <v>111.13846</v>
       </c>
     </row>
     <row r="59">
@@ -893,7 +893,15 @@
         <v>46203</v>
       </c>
       <c r="B59" t="n">
-        <v>110.22154</v>
+        <v>110.15775</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B60" t="n">
+        <v>109.91611</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/bcb_sgs_ibc_br_sa.xlsx
+++ b/data/final/series/bcb_sgs_ibc_br_sa.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B60"/>
+  <dimension ref="A1:B59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,473 +434,465 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="B2" t="n">
-        <v>96.96513</v>
+        <v>97.48671</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="B3" t="n">
-        <v>97.48671</v>
+        <v>99.05526</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44530</v>
+        <v>44561</v>
       </c>
       <c r="B4" t="n">
-        <v>99.05526</v>
+        <v>99.37716</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>44592</v>
       </c>
       <c r="B5" t="n">
-        <v>99.37716</v>
+        <v>97.4213</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44592</v>
+        <v>44620</v>
       </c>
       <c r="B6" t="n">
-        <v>97.4213</v>
+        <v>98.4804</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>44620</v>
+        <v>44651</v>
       </c>
       <c r="B7" t="n">
-        <v>98.4804</v>
+        <v>99.54801999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>44651</v>
+        <v>44681</v>
       </c>
       <c r="B8" t="n">
-        <v>99.54801999999999</v>
+        <v>99.44118</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>44681</v>
+        <v>44712</v>
       </c>
       <c r="B9" t="n">
-        <v>99.44118</v>
+        <v>99.6454</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>44712</v>
+        <v>44742</v>
       </c>
       <c r="B10" t="n">
-        <v>99.6454</v>
+        <v>99.51048</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>44742</v>
+        <v>44773</v>
       </c>
       <c r="B11" t="n">
-        <v>99.51048</v>
+        <v>101.43172</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>44773</v>
+        <v>44804</v>
       </c>
       <c r="B12" t="n">
-        <v>101.43172</v>
+        <v>101.10583</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>44804</v>
+        <v>44834</v>
       </c>
       <c r="B13" t="n">
-        <v>101.10583</v>
+        <v>101.16034</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>44834</v>
+        <v>44865</v>
       </c>
       <c r="B14" t="n">
-        <v>101.16034</v>
+        <v>101.44171</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>44865</v>
+        <v>44895</v>
       </c>
       <c r="B15" t="n">
-        <v>101.44171</v>
+        <v>100.7146</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>44895</v>
+        <v>44926</v>
       </c>
       <c r="B16" t="n">
-        <v>100.7146</v>
+        <v>100.58818</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>44926</v>
+        <v>44957</v>
       </c>
       <c r="B17" t="n">
-        <v>100.58818</v>
+        <v>100.10988</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>44957</v>
+        <v>44985</v>
       </c>
       <c r="B18" t="n">
-        <v>100.10988</v>
+        <v>103.07987</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>44985</v>
+        <v>45016</v>
       </c>
       <c r="B19" t="n">
-        <v>103.07987</v>
+        <v>103.08494</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45016</v>
+        <v>45046</v>
       </c>
       <c r="B20" t="n">
-        <v>103.08494</v>
+        <v>103.93573</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45046</v>
+        <v>45077</v>
       </c>
       <c r="B21" t="n">
-        <v>103.93573</v>
+        <v>102.42973</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45077</v>
+        <v>45107</v>
       </c>
       <c r="B22" t="n">
-        <v>102.42973</v>
+        <v>102.39935</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45107</v>
+        <v>45138</v>
       </c>
       <c r="B23" t="n">
-        <v>102.39935</v>
+        <v>102.90686</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45138</v>
+        <v>45169</v>
       </c>
       <c r="B24" t="n">
-        <v>102.90686</v>
+        <v>102.50239</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45169</v>
+        <v>45199</v>
       </c>
       <c r="B25" t="n">
-        <v>102.50239</v>
+        <v>102.5153</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45199</v>
+        <v>45230</v>
       </c>
       <c r="B26" t="n">
-        <v>102.5153</v>
+        <v>102.83959</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45230</v>
+        <v>45260</v>
       </c>
       <c r="B27" t="n">
-        <v>102.83959</v>
+        <v>103.59456</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45260</v>
+        <v>45291</v>
       </c>
       <c r="B28" t="n">
-        <v>103.59456</v>
+        <v>104.88818</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45291</v>
+        <v>45322</v>
       </c>
       <c r="B29" t="n">
-        <v>104.88818</v>
+        <v>104.473</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45322</v>
+        <v>45351</v>
       </c>
       <c r="B30" t="n">
-        <v>104.473</v>
+        <v>104.65885</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45351</v>
+        <v>45382</v>
       </c>
       <c r="B31" t="n">
-        <v>104.65885</v>
+        <v>104.6738</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45382</v>
+        <v>45412</v>
       </c>
       <c r="B32" t="n">
-        <v>104.6738</v>
+        <v>104.62771</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45412</v>
+        <v>45443</v>
       </c>
       <c r="B33" t="n">
-        <v>104.62771</v>
+        <v>105.60427</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45443</v>
+        <v>45473</v>
       </c>
       <c r="B34" t="n">
-        <v>105.60427</v>
+        <v>106.5891</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45473</v>
+        <v>45504</v>
       </c>
       <c r="B35" t="n">
-        <v>106.5891</v>
+        <v>107.06237</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45504</v>
+        <v>45535</v>
       </c>
       <c r="B36" t="n">
-        <v>107.06237</v>
+        <v>107.19174</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45535</v>
+        <v>45565</v>
       </c>
       <c r="B37" t="n">
-        <v>107.19174</v>
+        <v>108.04382</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45565</v>
+        <v>45596</v>
       </c>
       <c r="B38" t="n">
-        <v>108.04382</v>
+        <v>108.2446</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45596</v>
+        <v>45626</v>
       </c>
       <c r="B39" t="n">
-        <v>108.2446</v>
+        <v>108.00109</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45626</v>
+        <v>45657</v>
       </c>
       <c r="B40" t="n">
-        <v>108.00109</v>
+        <v>107.37012</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45657</v>
+        <v>45688</v>
       </c>
       <c r="B41" t="n">
-        <v>107.37012</v>
+        <v>108.09524</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45688</v>
+        <v>45716</v>
       </c>
       <c r="B42" t="n">
-        <v>108.09524</v>
+        <v>108.62006</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45716</v>
+        <v>45747</v>
       </c>
       <c r="B43" t="n">
-        <v>108.62006</v>
+        <v>110.03287</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45747</v>
+        <v>45777</v>
       </c>
       <c r="B44" t="n">
-        <v>110.03287</v>
+        <v>109.52766</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45777</v>
+        <v>45808</v>
       </c>
       <c r="B45" t="n">
-        <v>109.52766</v>
+        <v>108.8862</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45808</v>
+        <v>45838</v>
       </c>
       <c r="B46" t="n">
-        <v>108.8862</v>
+        <v>108.80376</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45838</v>
+        <v>45869</v>
       </c>
       <c r="B47" t="n">
-        <v>108.80376</v>
+        <v>108.49869</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45869</v>
+        <v>45900</v>
       </c>
       <c r="B48" t="n">
-        <v>108.49869</v>
+        <v>108.82893</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45900</v>
+        <v>45930</v>
       </c>
       <c r="B49" t="n">
-        <v>108.82893</v>
+        <v>108.73548</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45930</v>
+        <v>45961</v>
       </c>
       <c r="B50" t="n">
-        <v>108.73548</v>
+        <v>108.75326</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45961</v>
+        <v>45991</v>
       </c>
       <c r="B51" t="n">
-        <v>108.75326</v>
+        <v>109.25005</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45991</v>
+        <v>46022</v>
       </c>
       <c r="B52" t="n">
-        <v>109.25005</v>
+        <v>109.4528</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="B53" t="n">
-        <v>109.4528</v>
+        <v>110.04992</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B54" t="n">
-        <v>110.04992</v>
+        <v>110.7366</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46081</v>
+        <v>46112</v>
       </c>
       <c r="B55" t="n">
-        <v>110.7366</v>
+        <v>110.58808</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="B56" t="n">
-        <v>110.58808</v>
+        <v>110.90009</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="B57" t="n">
-        <v>110.90009</v>
+        <v>111.13846</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="B58" t="n">
-        <v>111.13846</v>
+        <v>110.15775</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="B59" t="n">
-        <v>110.15775</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="B60" t="n">
         <v>109.91611</v>
       </c>
     </row>

--- a/data/final/series/bcb_sgs_ibc_br_sa.xlsx
+++ b/data/final/series/bcb_sgs_ibc_br_sa.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B59"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,7 +437,7 @@
         <v>44500</v>
       </c>
       <c r="B2" t="n">
-        <v>97.48671</v>
+        <v>97.48845</v>
       </c>
     </row>
     <row r="3">
@@ -445,7 +445,7 @@
         <v>44530</v>
       </c>
       <c r="B3" t="n">
-        <v>99.05526</v>
+        <v>99.05624</v>
       </c>
     </row>
     <row r="4">
@@ -453,7 +453,7 @@
         <v>44561</v>
       </c>
       <c r="B4" t="n">
-        <v>99.37716</v>
+        <v>99.38482</v>
       </c>
     </row>
     <row r="5">
@@ -461,7 +461,7 @@
         <v>44592</v>
       </c>
       <c r="B5" t="n">
-        <v>97.4213</v>
+        <v>97.4208</v>
       </c>
     </row>
     <row r="6">
@@ -469,7 +469,7 @@
         <v>44620</v>
       </c>
       <c r="B6" t="n">
-        <v>98.4804</v>
+        <v>98.49135</v>
       </c>
     </row>
     <row r="7">
@@ -477,7 +477,7 @@
         <v>44651</v>
       </c>
       <c r="B7" t="n">
-        <v>99.54801999999999</v>
+        <v>99.56176000000001</v>
       </c>
     </row>
     <row r="8">
@@ -485,7 +485,7 @@
         <v>44681</v>
       </c>
       <c r="B8" t="n">
-        <v>99.44118</v>
+        <v>99.45421</v>
       </c>
     </row>
     <row r="9">
@@ -493,7 +493,7 @@
         <v>44712</v>
       </c>
       <c r="B9" t="n">
-        <v>99.6454</v>
+        <v>99.64297000000001</v>
       </c>
     </row>
     <row r="10">
@@ -501,7 +501,7 @@
         <v>44742</v>
       </c>
       <c r="B10" t="n">
-        <v>99.51048</v>
+        <v>99.49797</v>
       </c>
     </row>
     <row r="11">
@@ -509,7 +509,7 @@
         <v>44773</v>
       </c>
       <c r="B11" t="n">
-        <v>101.43172</v>
+        <v>101.41926</v>
       </c>
     </row>
     <row r="12">
@@ -517,7 +517,7 @@
         <v>44804</v>
       </c>
       <c r="B12" t="n">
-        <v>101.10583</v>
+        <v>101.10264</v>
       </c>
     </row>
     <row r="13">
@@ -525,7 +525,7 @@
         <v>44834</v>
       </c>
       <c r="B13" t="n">
-        <v>101.16034</v>
+        <v>101.1562</v>
       </c>
     </row>
     <row r="14">
@@ -533,7 +533,7 @@
         <v>44865</v>
       </c>
       <c r="B14" t="n">
-        <v>101.44171</v>
+        <v>101.43769</v>
       </c>
     </row>
     <row r="15">
@@ -541,7 +541,7 @@
         <v>44895</v>
       </c>
       <c r="B15" t="n">
-        <v>100.7146</v>
+        <v>100.71743</v>
       </c>
     </row>
     <row r="16">
@@ -549,7 +549,7 @@
         <v>44926</v>
       </c>
       <c r="B16" t="n">
-        <v>100.58818</v>
+        <v>100.59088</v>
       </c>
     </row>
     <row r="17">
@@ -557,7 +557,7 @@
         <v>44957</v>
       </c>
       <c r="B17" t="n">
-        <v>100.10988</v>
+        <v>100.10409</v>
       </c>
     </row>
     <row r="18">
@@ -565,7 +565,7 @@
         <v>44985</v>
       </c>
       <c r="B18" t="n">
-        <v>103.07987</v>
+        <v>103.08488</v>
       </c>
     </row>
     <row r="19">
@@ -573,7 +573,7 @@
         <v>45016</v>
       </c>
       <c r="B19" t="n">
-        <v>103.08494</v>
+        <v>103.09631</v>
       </c>
     </row>
     <row r="20">
@@ -581,7 +581,7 @@
         <v>45046</v>
       </c>
       <c r="B20" t="n">
-        <v>103.93573</v>
+        <v>103.92975</v>
       </c>
     </row>
     <row r="21">
@@ -589,7 +589,7 @@
         <v>45077</v>
       </c>
       <c r="B21" t="n">
-        <v>102.42973</v>
+        <v>102.42356</v>
       </c>
     </row>
     <row r="22">
@@ -597,7 +597,7 @@
         <v>45107</v>
       </c>
       <c r="B22" t="n">
-        <v>102.39935</v>
+        <v>102.38761</v>
       </c>
     </row>
     <row r="23">
@@ -605,7 +605,7 @@
         <v>45138</v>
       </c>
       <c r="B23" t="n">
-        <v>102.90686</v>
+        <v>102.90097</v>
       </c>
     </row>
     <row r="24">
@@ -613,7 +613,7 @@
         <v>45169</v>
       </c>
       <c r="B24" t="n">
-        <v>102.50239</v>
+        <v>102.49883</v>
       </c>
     </row>
     <row r="25">
@@ -621,7 +621,7 @@
         <v>45199</v>
       </c>
       <c r="B25" t="n">
-        <v>102.5153</v>
+        <v>102.5197</v>
       </c>
     </row>
     <row r="26">
@@ -629,7 +629,7 @@
         <v>45230</v>
       </c>
       <c r="B26" t="n">
-        <v>102.83959</v>
+        <v>102.8499</v>
       </c>
     </row>
     <row r="27">
@@ -637,7 +637,7 @@
         <v>45260</v>
       </c>
       <c r="B27" t="n">
-        <v>103.59456</v>
+        <v>103.60561</v>
       </c>
     </row>
     <row r="28">
@@ -645,7 +645,7 @@
         <v>45291</v>
       </c>
       <c r="B28" t="n">
-        <v>104.88818</v>
+        <v>104.8968</v>
       </c>
     </row>
     <row r="29">
@@ -653,7 +653,7 @@
         <v>45322</v>
       </c>
       <c r="B29" t="n">
-        <v>104.473</v>
+        <v>104.46088</v>
       </c>
     </row>
     <row r="30">
@@ -661,7 +661,7 @@
         <v>45351</v>
       </c>
       <c r="B30" t="n">
-        <v>104.65885</v>
+        <v>104.65783</v>
       </c>
     </row>
     <row r="31">
@@ -669,7 +669,7 @@
         <v>45382</v>
       </c>
       <c r="B31" t="n">
-        <v>104.6738</v>
+        <v>104.68489</v>
       </c>
     </row>
     <row r="32">
@@ -677,7 +677,7 @@
         <v>45412</v>
       </c>
       <c r="B32" t="n">
-        <v>104.62771</v>
+        <v>104.62189</v>
       </c>
     </row>
     <row r="33">
@@ -685,7 +685,7 @@
         <v>45443</v>
       </c>
       <c r="B33" t="n">
-        <v>105.60427</v>
+        <v>105.5883</v>
       </c>
     </row>
     <row r="34">
@@ -693,7 +693,7 @@
         <v>45473</v>
       </c>
       <c r="B34" t="n">
-        <v>106.5891</v>
+        <v>106.56647</v>
       </c>
     </row>
     <row r="35">
@@ -701,7 +701,7 @@
         <v>45504</v>
       </c>
       <c r="B35" t="n">
-        <v>107.06237</v>
+        <v>107.07017</v>
       </c>
     </row>
     <row r="36">
@@ -709,7 +709,7 @@
         <v>45535</v>
       </c>
       <c r="B36" t="n">
-        <v>107.19174</v>
+        <v>107.19578</v>
       </c>
     </row>
     <row r="37">
@@ -717,7 +717,7 @@
         <v>45565</v>
       </c>
       <c r="B37" t="n">
-        <v>108.04382</v>
+        <v>108.05141</v>
       </c>
     </row>
     <row r="38">
@@ -725,7 +725,7 @@
         <v>45596</v>
       </c>
       <c r="B38" t="n">
-        <v>108.2446</v>
+        <v>108.26621</v>
       </c>
     </row>
     <row r="39">
@@ -733,7 +733,7 @@
         <v>45626</v>
       </c>
       <c r="B39" t="n">
-        <v>108.00109</v>
+        <v>108.02232</v>
       </c>
     </row>
     <row r="40">
@@ -741,7 +741,7 @@
         <v>45657</v>
       </c>
       <c r="B40" t="n">
-        <v>107.37012</v>
+        <v>107.37891</v>
       </c>
     </row>
     <row r="41">
@@ -749,7 +749,7 @@
         <v>45688</v>
       </c>
       <c r="B41" t="n">
-        <v>108.09524</v>
+        <v>108.05509</v>
       </c>
     </row>
     <row r="42">
@@ -757,7 +757,7 @@
         <v>45716</v>
       </c>
       <c r="B42" t="n">
-        <v>108.62006</v>
+        <v>108.57481</v>
       </c>
     </row>
     <row r="43">
@@ -765,7 +765,7 @@
         <v>45747</v>
       </c>
       <c r="B43" t="n">
-        <v>110.03287</v>
+        <v>110.03087</v>
       </c>
     </row>
     <row r="44">
@@ -773,7 +773,7 @@
         <v>45777</v>
       </c>
       <c r="B44" t="n">
-        <v>109.52766</v>
+        <v>109.51799</v>
       </c>
     </row>
     <row r="45">
@@ -781,7 +781,7 @@
         <v>45808</v>
       </c>
       <c r="B45" t="n">
-        <v>108.8862</v>
+        <v>108.88849</v>
       </c>
     </row>
     <row r="46">
@@ -789,7 +789,7 @@
         <v>45838</v>
       </c>
       <c r="B46" t="n">
-        <v>108.80376</v>
+        <v>108.82565</v>
       </c>
     </row>
     <row r="47">
@@ -797,7 +797,7 @@
         <v>45869</v>
       </c>
       <c r="B47" t="n">
-        <v>108.49869</v>
+        <v>108.60295</v>
       </c>
     </row>
     <row r="48">
@@ -805,7 +805,7 @@
         <v>45900</v>
       </c>
       <c r="B48" t="n">
-        <v>108.82893</v>
+        <v>108.84223</v>
       </c>
     </row>
     <row r="49">
@@ -813,7 +813,7 @@
         <v>45930</v>
       </c>
       <c r="B49" t="n">
-        <v>108.73548</v>
+        <v>108.7154</v>
       </c>
     </row>
     <row r="50">
@@ -821,7 +821,7 @@
         <v>45961</v>
       </c>
       <c r="B50" t="n">
-        <v>108.75326</v>
+        <v>108.73877</v>
       </c>
     </row>
     <row r="51">
@@ -829,7 +829,7 @@
         <v>45991</v>
       </c>
       <c r="B51" t="n">
-        <v>109.25005</v>
+        <v>109.25356</v>
       </c>
     </row>
     <row r="52">
@@ -837,7 +837,7 @@
         <v>46022</v>
       </c>
       <c r="B52" t="n">
-        <v>109.4528</v>
+        <v>109.47578</v>
       </c>
     </row>
     <row r="53">
@@ -845,7 +845,7 @@
         <v>46053</v>
       </c>
       <c r="B53" t="n">
-        <v>110.04992</v>
+        <v>110.15169</v>
       </c>
     </row>
     <row r="54">
@@ -853,7 +853,7 @@
         <v>46081</v>
       </c>
       <c r="B54" t="n">
-        <v>110.7366</v>
+        <v>110.82485</v>
       </c>
     </row>
     <row r="55">
@@ -861,7 +861,7 @@
         <v>46112</v>
       </c>
       <c r="B55" t="n">
-        <v>110.58808</v>
+        <v>110.65755</v>
       </c>
     </row>
     <row r="56">
@@ -869,7 +869,7 @@
         <v>46142</v>
       </c>
       <c r="B56" t="n">
-        <v>110.90009</v>
+        <v>111.04254</v>
       </c>
     </row>
     <row r="57">
@@ -877,7 +877,7 @@
         <v>46173</v>
       </c>
       <c r="B57" t="n">
-        <v>111.13846</v>
+        <v>111.25061</v>
       </c>
     </row>
     <row r="58">
@@ -885,7 +885,7 @@
         <v>46203</v>
       </c>
       <c r="B58" t="n">
-        <v>110.15775</v>
+        <v>110.37352</v>
       </c>
     </row>
     <row r="59">
@@ -893,7 +893,15 @@
         <v>46234</v>
       </c>
       <c r="B59" t="n">
-        <v>109.91611</v>
+        <v>110.03188</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B60" t="n">
+        <v>110.40624</v>
       </c>
     </row>
   </sheetData>
